--- a/Documents/ProvdierInformation.xlsx
+++ b/Documents/ProvdierInformation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SuperCRM\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4987C235-831C-4BBC-8525-EE1A962178BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73826C05-C86E-4BBD-BCB5-9ABDB9404EB7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6520" xr2:uid="{A6B8B728-556A-4E72-872A-53EADE7EF3B6}"/>
   </bookViews>
@@ -440,6 +440,7 @@
     <col min="1" max="1" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
